--- a/Data/Process6_Configuration.xlsx
+++ b/Data/Process6_Configuration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ui_Robot1\Documents\UiPath\Project Cost Data (Dev)\Process 6 - Insert Temporary Transaction Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0505B7-A391-40BC-82B2-F709902F784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145AFA49-A6D5-4A48-BBD5-ED17ACF8333D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-2050" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StoredConfig" sheetId="1" r:id="rId1"/>
@@ -2130,15 +2130,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005466DA3702E1A14681A7752EFBDA10D8" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a8491fcfc1575a34af03aaf041f1b1c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82bfd1a8-954c-439e-a286-ef353ebc026f" xmlns:ns3="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7731705f95507e2ea5a143a26fe9bb84" ns2:_="" ns3:_="">
     <xsd:import namespace="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
@@ -2327,6 +2318,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1877DE71-B900-40F8-975E-FA93107C4206}">
   <ds:schemaRefs>
@@ -2339,14 +2339,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{086E1D7E-780C-4B3A-B8DD-9EEA6C8BE49F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72F20432-C984-48FD-88B0-817F9F1FC1AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2363,4 +2355,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{086E1D7E-780C-4B3A-B8DD-9EEA6C8BE49F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Data/Process6_Configuration.xlsx
+++ b/Data/Process6_Configuration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ui_Robot1\Documents\UiPath\Project Cost Data (Dev)\Process 6 - Insert Temporary Transaction Process\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145AFA49-A6D5-4A48-BBD5-ED17ACF8333D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18B6AE8-3315-4449-A878-4FB850AA6B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2119,17 +2119,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82bfd1a8-954c-439e-a286-ef353ebc026f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005466DA3702E1A14681A7752EFBDA10D8" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a8491fcfc1575a34af03aaf041f1b1c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82bfd1a8-954c-439e-a286-ef353ebc026f" xmlns:ns3="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7731705f95507e2ea5a143a26fe9bb84" ns2:_="" ns3:_="">
     <xsd:import namespace="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
@@ -2318,6 +2307,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82bfd1a8-954c-439e-a286-ef353ebc026f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2328,17 +2328,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1877DE71-B900-40F8-975E-FA93107C4206}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
-    <ds:schemaRef ds:uri="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72F20432-C984-48FD-88B0-817F9F1FC1AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2357,6 +2346,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1877DE71-B900-40F8-975E-FA93107C4206}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="82bfd1a8-954c-439e-a286-ef353ebc026f"/>
+    <ds:schemaRef ds:uri="5e1c2f93-a2fb-4cf1-9521-08720b4e64d5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{086E1D7E-780C-4B3A-B8DD-9EEA6C8BE49F}">
   <ds:schemaRefs>
